--- a/模板_单产品成本归集表.xlsx
+++ b/模板_单产品成本归集表.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,7 +28,13 @@
     <font>
       <name val="微软雅黑"/>
       <b val="1"/>
-      <color rgb="001e3a5f"/>
+      <color rgb="001E3A5F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -36,15 +42,45 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001e3a5f"/>
+        <bgColor rgb="001e3a5f"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
+        <bgColor rgb="00F59E0B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007C3AED"/>
+        <bgColor rgb="007C3AED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,14 +88,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.4" customWidth="1" min="1" max="1"/>
@@ -474,81 +535,75 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>不锈钢板304</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>2.0x1500x3000mm</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>铝合金型材</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>6063-T5 40x40</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>碳钢板Q235</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>3.0x1250x2500mm</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -561,199 +616,128 @@
       <c r="E7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>工序/工种</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>工时(小时)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>小时工资率(¥/h)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>下料操作工</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>焊接工</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>装配工</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>质检员</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="n"/>
-      <c r="E13" s="1" t="n"/>
-    </row>
+    </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>--- 制造费用 ---</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="1" t="n"/>
+      <c r="E14" s="1" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>费用总额(¥)</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>预计产量(件)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>分配方法</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>单位制造费用(¥/件)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n"/>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>按工时</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="1" t="n"/>
-      <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="n"/>
-      <c r="E17" s="1" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>--- 计算结果 ---</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>单位直接材料</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>单位直接人工</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>单位制造费用</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>单位产品成本</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>18750</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>7700</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>上传到工具自动计算</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
